--- a/model/data/invoice/sale/1405-03-30-sale-zibavash-express.xlsx
+++ b/model/data/invoice/sale/1405-03-30-sale-zibavash-express.xlsx
@@ -441,22 +441,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v xml:space="preserve">رژ مو گلدن رز مدل Medium Brown </v>
+        <v xml:space="preserve">رژ مو گلدن رز مدل Brown </v>
       </c>
       <c r="B3">
-        <v>33868475</v>
+        <v>33869152</v>
       </c>
       <c r="C3">
-        <v>756399</v>
+        <v>759485</v>
       </c>
       <c r="D3">
-        <v>5810000</v>
+        <v>6035900</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>00221197</v>
+        <v>00221199</v>
       </c>
     </row>
   </sheetData>
